--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251023_201315.xlsx
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
